--- a/news_daily/2026-09-03.xlsx
+++ b/news_daily/2026-09-03.xlsx
@@ -1482,28 +1482,32 @@
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -1547,7 +1551,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
@@ -1556,7 +1560,11 @@
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>e24a24d6eb8f401e8af44271007979f7</t>
+        </is>
+      </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
           <t>2e3733b74a0206c987a812b0</t>
@@ -1577,7 +1585,11 @@
       <c r="AL5" s="3" t="inlineStr"/>
       <c r="AM5" s="3" t="inlineStr"/>
       <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="3" t="inlineStr"/>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr"/>
@@ -1621,10 +1633,22 @@
         </is>
       </c>
       <c r="BH5" s="3" t="inlineStr"/>
-      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ5" s="3" t="inlineStr"/>
-      <c r="BK5" s="3" t="inlineStr"/>
-      <c r="BL5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -1660,28 +1684,32 @@
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1725,7 +1753,7 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
@@ -1734,7 +1762,11 @@
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>48efbd369ab04f5ab4e7659272f2b2fe</t>
+        </is>
+      </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
           <t>8d4b43099025a11a21b18110</t>
@@ -1755,7 +1787,11 @@
       <c r="AL6" s="3" t="inlineStr"/>
       <c r="AM6" s="3" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="3" t="inlineStr"/>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr"/>
@@ -1799,10 +1835,22 @@
         </is>
       </c>
       <c r="BH6" s="3" t="inlineStr"/>
-      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ6" s="3" t="inlineStr"/>
-      <c r="BK6" s="3" t="inlineStr"/>
-      <c r="BL6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -2634,28 +2682,32 @@
       <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -2699,7 +2751,7 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
@@ -2708,7 +2760,11 @@
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr"/>
-      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>4105a80a4e004d6980b0ee412ce07827</t>
+        </is>
+      </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
           <t>74b0e0841982b4e48be28e18</t>
@@ -2729,7 +2785,11 @@
       <c r="AL11" s="3" t="inlineStr"/>
       <c r="AM11" s="3" t="inlineStr"/>
       <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="3" t="inlineStr"/>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr"/>
@@ -2773,10 +2833,22 @@
         </is>
       </c>
       <c r="BH11" s="3" t="inlineStr"/>
-      <c r="BI11" s="3" t="inlineStr"/>
+      <c r="BI11" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ11" s="3" t="inlineStr"/>
-      <c r="BK11" s="3" t="inlineStr"/>
-      <c r="BL11" s="3" t="inlineStr"/>
+      <c r="BK11" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -3010,28 +3082,32 @@
       <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -3075,7 +3151,7 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
@@ -3084,7 +3160,11 @@
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr"/>
-      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>c2a13c4849d44778ad85e71ea616fdad</t>
+        </is>
+      </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
           <t>b3a441042df5b1a580820fb3</t>
@@ -3105,7 +3185,11 @@
       <c r="AL13" s="3" t="inlineStr"/>
       <c r="AM13" s="3" t="inlineStr"/>
       <c r="AN13" s="3" t="inlineStr"/>
-      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="3" t="inlineStr"/>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr"/>
@@ -3149,10 +3233,22 @@
         </is>
       </c>
       <c r="BH13" s="3" t="inlineStr"/>
-      <c r="BI13" s="3" t="inlineStr"/>
+      <c r="BI13" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ13" s="3" t="inlineStr"/>
-      <c r="BK13" s="3" t="inlineStr"/>
-      <c r="BL13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -3188,28 +3284,32 @@
       <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -3253,7 +3353,7 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
@@ -3262,7 +3362,11 @@
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr"/>
-      <c r="AB14" s="3" t="inlineStr"/>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>5d5f490c0c0342ada16df56e7622c177</t>
+        </is>
+      </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
           <t>fc4199a2baf6e9b9ccb7359e</t>
@@ -3283,7 +3387,11 @@
       <c r="AL14" s="3" t="inlineStr"/>
       <c r="AM14" s="3" t="inlineStr"/>
       <c r="AN14" s="3" t="inlineStr"/>
-      <c r="AO14" s="3" t="inlineStr"/>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP14" s="3" t="inlineStr"/>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr"/>
@@ -3327,10 +3435,22 @@
         </is>
       </c>
       <c r="BH14" s="3" t="inlineStr"/>
-      <c r="BI14" s="3" t="inlineStr"/>
+      <c r="BI14" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ14" s="3" t="inlineStr"/>
-      <c r="BK14" s="3" t="inlineStr"/>
-      <c r="BL14" s="3" t="inlineStr"/>
+      <c r="BK14" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -4352,28 +4472,32 @@
       <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -4417,7 +4541,7 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
@@ -4426,7 +4550,11 @@
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr"/>
-      <c r="AB20" s="3" t="inlineStr"/>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>5dce66da3dc64e84818f93e98850085d</t>
+        </is>
+      </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
           <t>da469a1d28f98347793d725c</t>
@@ -4447,7 +4575,11 @@
       <c r="AL20" s="3" t="inlineStr"/>
       <c r="AM20" s="3" t="inlineStr"/>
       <c r="AN20" s="3" t="inlineStr"/>
-      <c r="AO20" s="3" t="inlineStr"/>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP20" s="3" t="inlineStr"/>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr"/>
@@ -4483,10 +4615,22 @@
         </is>
       </c>
       <c r="BH20" s="3" t="inlineStr"/>
-      <c r="BI20" s="3" t="inlineStr"/>
+      <c r="BI20" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ20" s="3" t="inlineStr"/>
-      <c r="BK20" s="3" t="inlineStr"/>
-      <c r="BL20" s="3" t="inlineStr"/>
+      <c r="BK20" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -4522,28 +4666,32 @@
       <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -4587,7 +4735,7 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
@@ -4596,7 +4744,11 @@
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr"/>
-      <c r="AB21" s="3" t="inlineStr"/>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>01136fb01875407ebbc9777b00252ef1</t>
+        </is>
+      </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
           <t>0c26f28795751406b9b536c8</t>
@@ -4617,7 +4769,11 @@
       <c r="AL21" s="3" t="inlineStr"/>
       <c r="AM21" s="3" t="inlineStr"/>
       <c r="AN21" s="3" t="inlineStr"/>
-      <c r="AO21" s="3" t="inlineStr"/>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP21" s="3" t="inlineStr"/>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr"/>
@@ -4661,10 +4817,22 @@
         </is>
       </c>
       <c r="BH21" s="3" t="inlineStr"/>
-      <c r="BI21" s="3" t="inlineStr"/>
+      <c r="BI21" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ21" s="3" t="inlineStr"/>
-      <c r="BK21" s="3" t="inlineStr"/>
-      <c r="BL21" s="3" t="inlineStr"/>
+      <c r="BK21" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -4700,28 +4868,32 @@
       <c r="G22" s="3" t="inlineStr"/>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -4765,7 +4937,7 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
@@ -4774,7 +4946,11 @@
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr"/>
-      <c r="AB22" s="3" t="inlineStr"/>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>5825ff2dcb364c2fbd93f392077d5714</t>
+        </is>
+      </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
           <t>20ee1001be02f3e763da5746</t>
@@ -4795,7 +4971,11 @@
       <c r="AL22" s="3" t="inlineStr"/>
       <c r="AM22" s="3" t="inlineStr"/>
       <c r="AN22" s="3" t="inlineStr"/>
-      <c r="AO22" s="3" t="inlineStr"/>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP22" s="3" t="inlineStr"/>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr"/>
@@ -4839,10 +5019,22 @@
         </is>
       </c>
       <c r="BH22" s="3" t="inlineStr"/>
-      <c r="BI22" s="3" t="inlineStr"/>
+      <c r="BI22" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ22" s="3" t="inlineStr"/>
-      <c r="BK22" s="3" t="inlineStr"/>
-      <c r="BL22" s="3" t="inlineStr"/>
+      <c r="BK22" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL22" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -5662,28 +5854,32 @@
       <c r="G27" s="3" t="inlineStr"/>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -5727,7 +5923,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
@@ -5736,7 +5932,11 @@
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr"/>
-      <c r="AB27" s="3" t="inlineStr"/>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>41d0aa19005b4a279093935f49e65328</t>
+        </is>
+      </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
           <t>888e12352eeaa2d02cf7ac1b</t>
@@ -5757,7 +5957,11 @@
       <c r="AL27" s="3" t="inlineStr"/>
       <c r="AM27" s="3" t="inlineStr"/>
       <c r="AN27" s="3" t="inlineStr"/>
-      <c r="AO27" s="3" t="inlineStr"/>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP27" s="3" t="inlineStr"/>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr"/>
@@ -5801,10 +6005,22 @@
         </is>
       </c>
       <c r="BH27" s="3" t="inlineStr"/>
-      <c r="BI27" s="3" t="inlineStr"/>
+      <c r="BI27" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ27" s="3" t="inlineStr"/>
-      <c r="BK27" s="3" t="inlineStr"/>
-      <c r="BL27" s="3" t="inlineStr"/>
+      <c r="BK27" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL27" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -6038,28 +6254,32 @@
       <c r="G29" s="3" t="inlineStr"/>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -6103,7 +6323,7 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
@@ -6112,7 +6332,11 @@
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr"/>
-      <c r="AB29" s="3" t="inlineStr"/>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>43e4554669f440dda4087fffa035cb18</t>
+        </is>
+      </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
           <t>aa22c71e7caf952e0e211cd4</t>
@@ -6133,7 +6357,11 @@
       <c r="AL29" s="3" t="inlineStr"/>
       <c r="AM29" s="3" t="inlineStr"/>
       <c r="AN29" s="3" t="inlineStr"/>
-      <c r="AO29" s="3" t="inlineStr"/>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP29" s="3" t="inlineStr"/>
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr"/>
@@ -6177,10 +6405,22 @@
         </is>
       </c>
       <c r="BH29" s="3" t="inlineStr"/>
-      <c r="BI29" s="3" t="inlineStr"/>
+      <c r="BI29" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ29" s="3" t="inlineStr"/>
-      <c r="BK29" s="3" t="inlineStr"/>
-      <c r="BL29" s="3" t="inlineStr"/>
+      <c r="BK29" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -6433,13 +6673,17 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -6492,7 +6736,11 @@
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr"/>
-      <c r="AB31" s="3" t="inlineStr"/>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>fd87a2e10a79468e98f55b15a2954037</t>
+        </is>
+      </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
           <t>0f6f62762e56e02a75743643</t>
@@ -6513,7 +6761,11 @@
       <c r="AL31" s="3" t="inlineStr"/>
       <c r="AM31" s="3" t="inlineStr"/>
       <c r="AN31" s="3" t="inlineStr"/>
-      <c r="AO31" s="3" t="inlineStr"/>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP31" s="3" t="inlineStr"/>
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr"/>
@@ -6559,8 +6811,16 @@
       <c r="BH31" s="3" t="inlineStr"/>
       <c r="BI31" s="3" t="inlineStr"/>
       <c r="BJ31" s="3" t="inlineStr"/>
-      <c r="BK31" s="3" t="inlineStr"/>
-      <c r="BL31" s="3" t="inlineStr"/>
+      <c r="BK31" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL31" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -6596,28 +6856,32 @@
       <c r="G32" s="3" t="inlineStr"/>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -6661,7 +6925,7 @@
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
@@ -6670,7 +6934,11 @@
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr"/>
-      <c r="AB32" s="3" t="inlineStr"/>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>3905500ae95c45ffa103de08c7b4f331</t>
+        </is>
+      </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
           <t>c7b7939dd5ead0dc0176e65b</t>
@@ -6691,7 +6959,11 @@
       <c r="AL32" s="3" t="inlineStr"/>
       <c r="AM32" s="3" t="inlineStr"/>
       <c r="AN32" s="3" t="inlineStr"/>
-      <c r="AO32" s="3" t="inlineStr"/>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP32" s="3" t="inlineStr"/>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr"/>
@@ -6735,10 +7007,22 @@
         </is>
       </c>
       <c r="BH32" s="3" t="inlineStr"/>
-      <c r="BI32" s="3" t="inlineStr"/>
+      <c r="BI32" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ32" s="3" t="inlineStr"/>
-      <c r="BK32" s="3" t="inlineStr"/>
-      <c r="BL32" s="3" t="inlineStr"/>
+      <c r="BK32" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -7360,28 +7644,32 @@
       <c r="G36" s="3" t="inlineStr"/>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -7425,7 +7713,7 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
@@ -7434,7 +7722,11 @@
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr"/>
-      <c r="AB36" s="3" t="inlineStr"/>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>3b34c29bf05741cabe2ae3f09dcf4236</t>
+        </is>
+      </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
           <t>559db0bd0d43c1ad14fccaba</t>
@@ -7455,7 +7747,11 @@
       <c r="AL36" s="3" t="inlineStr"/>
       <c r="AM36" s="3" t="inlineStr"/>
       <c r="AN36" s="3" t="inlineStr"/>
-      <c r="AO36" s="3" t="inlineStr"/>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP36" s="3" t="inlineStr"/>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr"/>
@@ -7499,10 +7795,22 @@
         </is>
       </c>
       <c r="BH36" s="3" t="inlineStr"/>
-      <c r="BI36" s="3" t="inlineStr"/>
+      <c r="BI36" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ36" s="3" t="inlineStr"/>
-      <c r="BK36" s="3" t="inlineStr"/>
-      <c r="BL36" s="3" t="inlineStr"/>
+      <c r="BK36" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL36" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -7538,28 +7846,32 @@
       <c r="G37" s="3" t="inlineStr"/>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -7603,7 +7915,7 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
@@ -7612,7 +7924,11 @@
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr"/>
-      <c r="AB37" s="3" t="inlineStr"/>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>2a3417b82166405ab72a57d812def7ff</t>
+        </is>
+      </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
           <t>5f65f06bc75ea3ef0dc9a56d</t>
@@ -7633,7 +7949,11 @@
       <c r="AL37" s="3" t="inlineStr"/>
       <c r="AM37" s="3" t="inlineStr"/>
       <c r="AN37" s="3" t="inlineStr"/>
-      <c r="AO37" s="3" t="inlineStr"/>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP37" s="3" t="inlineStr"/>
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr"/>
@@ -7677,10 +7997,22 @@
         </is>
       </c>
       <c r="BH37" s="3" t="inlineStr"/>
-      <c r="BI37" s="3" t="inlineStr"/>
+      <c r="BI37" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ37" s="3" t="inlineStr"/>
-      <c r="BK37" s="3" t="inlineStr"/>
-      <c r="BL37" s="3" t="inlineStr"/>
+      <c r="BK37" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL37" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -7716,28 +8048,32 @@
       <c r="G38" s="3" t="inlineStr"/>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -7781,7 +8117,7 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
@@ -7790,7 +8126,11 @@
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr"/>
-      <c r="AB38" s="3" t="inlineStr"/>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>518c3daa8318492392744a85caf66f31</t>
+        </is>
+      </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
           <t>d5935a5af59e60f6567e930b</t>
@@ -7811,7 +8151,11 @@
       <c r="AL38" s="3" t="inlineStr"/>
       <c r="AM38" s="3" t="inlineStr"/>
       <c r="AN38" s="3" t="inlineStr"/>
-      <c r="AO38" s="3" t="inlineStr"/>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP38" s="3" t="inlineStr"/>
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr"/>
@@ -7855,10 +8199,22 @@
         </is>
       </c>
       <c r="BH38" s="3" t="inlineStr"/>
-      <c r="BI38" s="3" t="inlineStr"/>
+      <c r="BI38" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ38" s="3" t="inlineStr"/>
-      <c r="BK38" s="3" t="inlineStr"/>
-      <c r="BL38" s="3" t="inlineStr"/>
+      <c r="BK38" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -7894,28 +8250,32 @@
       <c r="G39" s="3" t="inlineStr"/>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -7959,7 +8319,7 @@
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
@@ -7968,7 +8328,11 @@
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr"/>
-      <c r="AB39" s="3" t="inlineStr"/>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>886ceb750bdb4c21a7e2f45885db305d</t>
+        </is>
+      </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
           <t>864d905cee4c8e78ffecd779</t>
@@ -7989,7 +8353,11 @@
       <c r="AL39" s="3" t="inlineStr"/>
       <c r="AM39" s="3" t="inlineStr"/>
       <c r="AN39" s="3" t="inlineStr"/>
-      <c r="AO39" s="3" t="inlineStr"/>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP39" s="3" t="inlineStr"/>
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr"/>
@@ -8025,10 +8393,22 @@
         </is>
       </c>
       <c r="BH39" s="3" t="inlineStr"/>
-      <c r="BI39" s="3" t="inlineStr"/>
+      <c r="BI39" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ39" s="3" t="inlineStr"/>
-      <c r="BK39" s="3" t="inlineStr"/>
-      <c r="BL39" s="3" t="inlineStr"/>
+      <c r="BK39" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL39" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -8266,28 +8646,32 @@
       <c r="G41" s="3" t="inlineStr"/>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -8331,7 +8715,7 @@
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
@@ -8340,7 +8724,11 @@
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr"/>
-      <c r="AB41" s="3" t="inlineStr"/>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>acacb9dd726a4f91a3bc319f441ce8b0</t>
+        </is>
+      </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
           <t>a11a1f1ad5ddeb0a57326bac</t>
@@ -8361,7 +8749,11 @@
       <c r="AL41" s="3" t="inlineStr"/>
       <c r="AM41" s="3" t="inlineStr"/>
       <c r="AN41" s="3" t="inlineStr"/>
-      <c r="AO41" s="3" t="inlineStr"/>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP41" s="3" t="inlineStr"/>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr"/>
@@ -8405,10 +8797,22 @@
         </is>
       </c>
       <c r="BH41" s="3" t="inlineStr"/>
-      <c r="BI41" s="3" t="inlineStr"/>
+      <c r="BI41" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ41" s="3" t="inlineStr"/>
-      <c r="BK41" s="3" t="inlineStr"/>
-      <c r="BL41" s="3" t="inlineStr"/>
+      <c r="BK41" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL41" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -8646,28 +9050,32 @@
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -8711,7 +9119,7 @@
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
@@ -8720,7 +9128,11 @@
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr"/>
-      <c r="AB43" s="3" t="inlineStr"/>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>51db929487bc4d80887e206bdaac8487</t>
+        </is>
+      </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
           <t>778229ec66511502a70b4199</t>
@@ -8741,7 +9153,11 @@
       <c r="AL43" s="3" t="inlineStr"/>
       <c r="AM43" s="3" t="inlineStr"/>
       <c r="AN43" s="3" t="inlineStr"/>
-      <c r="AO43" s="3" t="inlineStr"/>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP43" s="3" t="inlineStr"/>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr"/>
@@ -8785,10 +9201,22 @@
         </is>
       </c>
       <c r="BH43" s="3" t="inlineStr"/>
-      <c r="BI43" s="3" t="inlineStr"/>
+      <c r="BI43" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ43" s="3" t="inlineStr"/>
-      <c r="BK43" s="3" t="inlineStr"/>
-      <c r="BL43" s="3" t="inlineStr"/>
+      <c r="BK43" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL43" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -9849,13 +10277,17 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L49" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
@@ -9908,7 +10340,11 @@
         </is>
       </c>
       <c r="AA49" s="3" t="inlineStr"/>
-      <c r="AB49" s="3" t="inlineStr"/>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>79b4faa248ff4782b680a3e8c07d3055</t>
+        </is>
+      </c>
       <c r="AC49" s="3" t="inlineStr">
         <is>
           <t>c785d8ce557ea65b19e93b07</t>
@@ -9929,7 +10365,11 @@
       <c r="AL49" s="3" t="inlineStr"/>
       <c r="AM49" s="3" t="inlineStr"/>
       <c r="AN49" s="3" t="inlineStr"/>
-      <c r="AO49" s="3" t="inlineStr"/>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP49" s="3" t="inlineStr"/>
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr"/>
@@ -9975,8 +10415,16 @@
       <c r="BH49" s="3" t="inlineStr"/>
       <c r="BI49" s="3" t="inlineStr"/>
       <c r="BJ49" s="3" t="inlineStr"/>
-      <c r="BK49" s="3" t="inlineStr"/>
-      <c r="BL49" s="3" t="inlineStr"/>
+      <c r="BK49" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL49" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -10391,13 +10839,17 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L52" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -10446,7 +10898,11 @@
         </is>
       </c>
       <c r="AA52" s="3" t="inlineStr"/>
-      <c r="AB52" s="3" t="inlineStr"/>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>95d4fe8148b14f3c84dcec3471227015</t>
+        </is>
+      </c>
       <c r="AC52" s="3" t="inlineStr">
         <is>
           <t>a8a0d4e0133f85e42059ca3e</t>
@@ -10467,7 +10923,11 @@
       <c r="AL52" s="3" t="inlineStr"/>
       <c r="AM52" s="3" t="inlineStr"/>
       <c r="AN52" s="3" t="inlineStr"/>
-      <c r="AO52" s="3" t="inlineStr"/>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP52" s="3" t="inlineStr"/>
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr"/>
@@ -10505,8 +10965,16 @@
       <c r="BH52" s="3" t="inlineStr"/>
       <c r="BI52" s="3" t="inlineStr"/>
       <c r="BJ52" s="3" t="inlineStr"/>
-      <c r="BK52" s="3" t="inlineStr"/>
-      <c r="BL52" s="3" t="inlineStr"/>
+      <c r="BK52" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL52" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -10542,28 +11010,32 @@
       <c r="G53" s="3" t="inlineStr"/>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L53" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -10603,7 +11075,7 @@
       </c>
       <c r="Y53" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z53" s="3" t="inlineStr">
@@ -10612,7 +11084,11 @@
         </is>
       </c>
       <c r="AA53" s="3" t="inlineStr"/>
-      <c r="AB53" s="3" t="inlineStr"/>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>456653e687da4e088802de7b896719dc</t>
+        </is>
+      </c>
       <c r="AC53" s="3" t="inlineStr">
         <is>
           <t>7dcf9a614d2230d024914e61</t>
@@ -10633,7 +11109,11 @@
       <c r="AL53" s="3" t="inlineStr"/>
       <c r="AM53" s="3" t="inlineStr"/>
       <c r="AN53" s="3" t="inlineStr"/>
-      <c r="AO53" s="3" t="inlineStr"/>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP53" s="3" t="inlineStr"/>
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr"/>
@@ -10669,10 +11149,22 @@
         </is>
       </c>
       <c r="BH53" s="3" t="inlineStr"/>
-      <c r="BI53" s="3" t="inlineStr"/>
+      <c r="BI53" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ53" s="3" t="inlineStr"/>
-      <c r="BK53" s="3" t="inlineStr"/>
-      <c r="BL53" s="3" t="inlineStr"/>
+      <c r="BK53" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL53" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -10708,28 +11200,32 @@
       <c r="G54" s="3" t="inlineStr"/>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L54" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -10769,7 +11265,7 @@
       </c>
       <c r="Y54" s="3" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z54" s="3" t="inlineStr">
@@ -10778,7 +11274,11 @@
         </is>
       </c>
       <c r="AA54" s="3" t="inlineStr"/>
-      <c r="AB54" s="3" t="inlineStr"/>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>2bd34fd8e7b7417493361fd65e9e0f01</t>
+        </is>
+      </c>
       <c r="AC54" s="3" t="inlineStr">
         <is>
           <t>a2a410efc959c2f136cd0ec6</t>
@@ -10799,7 +11299,11 @@
       <c r="AL54" s="3" t="inlineStr"/>
       <c r="AM54" s="3" t="inlineStr"/>
       <c r="AN54" s="3" t="inlineStr"/>
-      <c r="AO54" s="3" t="inlineStr"/>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP54" s="3" t="inlineStr"/>
       <c r="AQ54" s="3" t="inlineStr"/>
       <c r="AR54" s="3" t="inlineStr"/>
@@ -10843,10 +11347,22 @@
         </is>
       </c>
       <c r="BH54" s="3" t="inlineStr"/>
-      <c r="BI54" s="3" t="inlineStr"/>
+      <c r="BI54" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ54" s="3" t="inlineStr"/>
-      <c r="BK54" s="3" t="inlineStr"/>
-      <c r="BL54" s="3" t="inlineStr"/>
+      <c r="BK54" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL54" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -10882,28 +11398,32 @@
       <c r="G55" s="3" t="inlineStr"/>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L55" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
@@ -10943,7 +11463,7 @@
       </c>
       <c r="Y55" s="3" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z55" s="3" t="inlineStr">
@@ -10952,7 +11472,11 @@
         </is>
       </c>
       <c r="AA55" s="3" t="inlineStr"/>
-      <c r="AB55" s="3" t="inlineStr"/>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>5d13e2a5735c43c48260b3cefb0212ae</t>
+        </is>
+      </c>
       <c r="AC55" s="3" t="inlineStr">
         <is>
           <t>1372ae9f8cdeb6fdebcb9e72</t>
@@ -10973,7 +11497,11 @@
       <c r="AL55" s="3" t="inlineStr"/>
       <c r="AM55" s="3" t="inlineStr"/>
       <c r="AN55" s="3" t="inlineStr"/>
-      <c r="AO55" s="3" t="inlineStr"/>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP55" s="3" t="inlineStr"/>
       <c r="AQ55" s="3" t="inlineStr"/>
       <c r="AR55" s="3" t="inlineStr"/>
@@ -11017,10 +11545,22 @@
         </is>
       </c>
       <c r="BH55" s="3" t="inlineStr"/>
-      <c r="BI55" s="3" t="inlineStr"/>
+      <c r="BI55" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ55" s="3" t="inlineStr"/>
-      <c r="BK55" s="3" t="inlineStr"/>
-      <c r="BL55" s="3" t="inlineStr"/>
+      <c r="BK55" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL55" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -11056,28 +11596,32 @@
       <c r="G56" s="3" t="inlineStr"/>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L56" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
@@ -11117,7 +11661,7 @@
       </c>
       <c r="Y56" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z56" s="3" t="inlineStr">
@@ -11126,7 +11670,11 @@
         </is>
       </c>
       <c r="AA56" s="3" t="inlineStr"/>
-      <c r="AB56" s="3" t="inlineStr"/>
+      <c r="AB56" s="3" t="inlineStr">
+        <is>
+          <t>11f99cf370f247719a77f8ef182f43e0</t>
+        </is>
+      </c>
       <c r="AC56" s="3" t="inlineStr">
         <is>
           <t>ccc87a074b8eae056a226606</t>
@@ -11147,7 +11695,11 @@
       <c r="AL56" s="3" t="inlineStr"/>
       <c r="AM56" s="3" t="inlineStr"/>
       <c r="AN56" s="3" t="inlineStr"/>
-      <c r="AO56" s="3" t="inlineStr"/>
+      <c r="AO56" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP56" s="3" t="inlineStr"/>
       <c r="AQ56" s="3" t="inlineStr"/>
       <c r="AR56" s="3" t="inlineStr"/>
@@ -11191,10 +11743,22 @@
         </is>
       </c>
       <c r="BH56" s="3" t="inlineStr"/>
-      <c r="BI56" s="3" t="inlineStr"/>
+      <c r="BI56" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ56" s="3" t="inlineStr"/>
-      <c r="BK56" s="3" t="inlineStr"/>
-      <c r="BL56" s="3" t="inlineStr"/>
+      <c r="BK56" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL56" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -11230,28 +11794,32 @@
       <c r="G57" s="3" t="inlineStr"/>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L57" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
@@ -11291,7 +11859,7 @@
       </c>
       <c r="Y57" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z57" s="3" t="inlineStr">
@@ -11300,7 +11868,11 @@
         </is>
       </c>
       <c r="AA57" s="3" t="inlineStr"/>
-      <c r="AB57" s="3" t="inlineStr"/>
+      <c r="AB57" s="3" t="inlineStr">
+        <is>
+          <t>cc78a596a0dd47e7b739116d75b28335</t>
+        </is>
+      </c>
       <c r="AC57" s="3" t="inlineStr">
         <is>
           <t>72b04947231e1b9773d4a24a</t>
@@ -11321,7 +11893,11 @@
       <c r="AL57" s="3" t="inlineStr"/>
       <c r="AM57" s="3" t="inlineStr"/>
       <c r="AN57" s="3" t="inlineStr"/>
-      <c r="AO57" s="3" t="inlineStr"/>
+      <c r="AO57" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP57" s="3" t="inlineStr"/>
       <c r="AQ57" s="3" t="inlineStr"/>
       <c r="AR57" s="3" t="inlineStr"/>
@@ -11357,10 +11933,22 @@
         </is>
       </c>
       <c r="BH57" s="3" t="inlineStr"/>
-      <c r="BI57" s="3" t="inlineStr"/>
+      <c r="BI57" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ57" s="3" t="inlineStr"/>
-      <c r="BK57" s="3" t="inlineStr"/>
-      <c r="BL57" s="3" t="inlineStr"/>
+      <c r="BK57" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL57" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -11411,13 +11999,17 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L58" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
@@ -11466,7 +12058,11 @@
         </is>
       </c>
       <c r="AA58" s="3" t="inlineStr"/>
-      <c r="AB58" s="3" t="inlineStr"/>
+      <c r="AB58" s="3" t="inlineStr">
+        <is>
+          <t>8d5cc8a316b54e1d8687c5321cd33abc</t>
+        </is>
+      </c>
       <c r="AC58" s="3" t="inlineStr">
         <is>
           <t>91bed686e9e5a43bee71dc61</t>
@@ -11487,7 +12083,11 @@
       <c r="AL58" s="3" t="inlineStr"/>
       <c r="AM58" s="3" t="inlineStr"/>
       <c r="AN58" s="3" t="inlineStr"/>
-      <c r="AO58" s="3" t="inlineStr"/>
+      <c r="AO58" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP58" s="3" t="inlineStr"/>
       <c r="AQ58" s="3" t="inlineStr"/>
       <c r="AR58" s="3" t="inlineStr"/>
@@ -11533,8 +12133,16 @@
       <c r="BH58" s="3" t="inlineStr"/>
       <c r="BI58" s="3" t="inlineStr"/>
       <c r="BJ58" s="3" t="inlineStr"/>
-      <c r="BK58" s="3" t="inlineStr"/>
-      <c r="BL58" s="3" t="inlineStr"/>
+      <c r="BK58" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL58" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -13628,28 +14236,32 @@
       <c r="G70" s="3" t="inlineStr"/>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L70" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
@@ -13689,7 +14301,7 @@
       </c>
       <c r="Y70" s="3" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z70" s="3" t="inlineStr">
@@ -13698,7 +14310,11 @@
         </is>
       </c>
       <c r="AA70" s="3" t="inlineStr"/>
-      <c r="AB70" s="3" t="inlineStr"/>
+      <c r="AB70" s="3" t="inlineStr">
+        <is>
+          <t>e03a3b2da7fb460e9111f52b52338f0b</t>
+        </is>
+      </c>
       <c r="AC70" s="3" t="inlineStr">
         <is>
           <t>f3c38a9e7064cfaa8ee4b298</t>
@@ -13719,7 +14335,11 @@
       <c r="AL70" s="3" t="inlineStr"/>
       <c r="AM70" s="3" t="inlineStr"/>
       <c r="AN70" s="3" t="inlineStr"/>
-      <c r="AO70" s="3" t="inlineStr"/>
+      <c r="AO70" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP70" s="3" t="inlineStr"/>
       <c r="AQ70" s="3" t="inlineStr"/>
       <c r="AR70" s="3" t="inlineStr"/>
@@ -13755,10 +14375,22 @@
         </is>
       </c>
       <c r="BH70" s="3" t="inlineStr"/>
-      <c r="BI70" s="3" t="inlineStr"/>
+      <c r="BI70" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ70" s="3" t="inlineStr"/>
-      <c r="BK70" s="3" t="inlineStr"/>
-      <c r="BL70" s="3" t="inlineStr"/>
+      <c r="BK70" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL70" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">

--- a/news_daily/2026-09-03.xlsx
+++ b/news_daily/2026-09-03.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$72</definedName>
@@ -27,16 +27,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -66,7 +63,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -74,21 +71,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -12523,7 +12512,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Boeing</t>
@@ -12673,7 +12666,11 @@
       <c r="BF61" s="2" t="inlineStr"/>
       <c r="BG61" s="2" t="inlineStr"/>
       <c r="BH61" s="2" t="inlineStr"/>
-      <c r="BI61" s="2" t="inlineStr"/>
+      <c r="BI61" s="2" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
       <c r="BJ61" s="2" t="inlineStr"/>
       <c r="BK61" s="2" t="inlineStr">
         <is>
@@ -17534,7 +17531,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Boeing</t>
@@ -17684,7 +17685,11 @@
       <c r="BF14" s="2" t="inlineStr"/>
       <c r="BG14" s="2" t="inlineStr"/>
       <c r="BH14" s="2" t="inlineStr"/>
-      <c r="BI14" s="2" t="inlineStr"/>
+      <c r="BI14" s="2" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
       <c r="BJ14" s="2" t="inlineStr"/>
       <c r="BK14" s="2" t="inlineStr">
         <is>
